--- a/research/traditional_assets/database/data/france/france_utility_water.xlsx
+++ b/research/traditional_assets/database/data/france/france_utility_water.xlsx
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.03821060046375647</v>
+        <v>0.07190344469406085</v>
       </c>
       <c r="AB2">
-        <v>0.03821060046375647</v>
+        <v>0.07190344469406085</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.03821060046375647</v>
+        <v>0.07190344469406085</v>
       </c>
       <c r="AB3">
-        <v>0.03821060046375647</v>
+        <v>0.07190344469406085</v>
       </c>
       <c r="AD3">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_utility_water.xlsx
+++ b/research/traditional_assets/database/data/france/france_utility_water.xlsx
@@ -588,50 +588,53 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.06309999999999999</v>
+        <v>-0.143</v>
       </c>
       <c r="E2">
-        <v>-0.209</v>
+        <v>-0.131</v>
       </c>
       <c r="G2">
-        <v>-0.01506369426751592</v>
+        <v>-0.003262032085561497</v>
       </c>
       <c r="H2">
-        <v>-0.01506369426751592</v>
+        <v>-0.003262032085561497</v>
       </c>
       <c r="I2">
-        <v>-0.02926751592356688</v>
+        <v>-0.02561497326203209</v>
       </c>
       <c r="J2">
-        <v>-0.02072456532966087</v>
+        <v>-0.01851551462335776</v>
       </c>
       <c r="K2">
-        <v>0.654</v>
+        <v>1.17</v>
       </c>
       <c r="L2">
-        <v>0.02082802547770701</v>
+        <v>0.06256684491978609</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.17066</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.06503666666666667</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.000564102564103</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.17066</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.06503666666666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.000564102564103</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
         <v>0</v>
       </c>
@@ -639,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.07190344469406085</v>
+        <v>0.0613871474445559</v>
       </c>
       <c r="AB2">
-        <v>0.07190344469406085</v>
+        <v>0.0613871474445559</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,19 +666,22 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AM2">
-        <v>-0.007</v>
+        <v>0.022</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
+      <c r="AO2">
+        <v>-21.77272727272727</v>
+      </c>
       <c r="AP2">
         <v>-0</v>
       </c>
       <c r="AQ2">
-        <v>131.2857142857143</v>
+        <v>-21.77272727272727</v>
       </c>
     </row>
     <row r="3">
@@ -695,50 +701,53 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.06309999999999999</v>
+        <v>-0.143</v>
       </c>
       <c r="E3">
-        <v>-0.209</v>
+        <v>-0.131</v>
       </c>
       <c r="G3">
-        <v>-0.01506369426751592</v>
+        <v>-0.003262032085561497</v>
       </c>
       <c r="H3">
-        <v>-0.01506369426751592</v>
+        <v>-0.003262032085561497</v>
       </c>
       <c r="I3">
-        <v>-0.02926751592356688</v>
+        <v>-0.02561497326203209</v>
       </c>
       <c r="J3">
-        <v>-0.02072456532966087</v>
+        <v>-0.01851551462335776</v>
       </c>
       <c r="K3">
-        <v>0.654</v>
+        <v>1.17</v>
       </c>
       <c r="L3">
-        <v>0.02082802547770701</v>
+        <v>0.06256684491978609</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.17066</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06503666666666667</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.000564102564103</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.17066</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06503666666666667</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.000564102564103</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
@@ -746,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.07190344469406085</v>
+        <v>0.0613871474445559</v>
       </c>
       <c r="AB3">
-        <v>0.07190344469406085</v>
+        <v>0.0613871474445559</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -770,19 +779,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AM3">
-        <v>-0.007</v>
+        <v>0.022</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
+      <c r="AO3">
+        <v>-21.77272727272727</v>
+      </c>
       <c r="AP3">
         <v>-0</v>
       </c>
       <c r="AQ3">
-        <v>131.2857142857143</v>
+        <v>-21.77272727272727</v>
       </c>
     </row>
   </sheetData>
